--- a/data/trans_orig/IP17-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77024</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>90134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>65472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80178</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147509</t>
+          <t>147360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166599</t>
+          <t>166636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>51809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57206</t>
+          <t>56957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>70816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60078</t>
+          <t>58949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71999</t>
+          <t>72262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120526</t>
+          <t>121550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138692</t>
+          <t>139355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39946</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60289</t>
+          <t>60066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71418</t>
+          <t>72682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>84956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126778</t>
+          <t>126335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>143156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49850</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>58885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77044</t>
+          <t>75764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102095</t>
+          <t>102642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150883</t>
+          <t>151296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170058</t>
+          <t>169358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143662</t>
+          <t>143189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162982</t>
+          <t>162722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300712</t>
+          <t>300165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325763</t>
+          <t>327043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26920</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77200</t>
+          <t>76809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89580</t>
+          <t>90077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98349</t>
+          <t>98813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111852</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178957</t>
+          <t>178986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198262</t>
+          <t>198398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21748</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58593</t>
+          <t>59115</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>68708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48177</t>
+          <t>46642</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59739</t>
+          <t>58820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109956</t>
+          <t>109938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125814</t>
+          <t>125514</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109408</t>
+          <t>107802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141796</t>
+          <t>140091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135704</t>
+          <t>136460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171784</t>
+          <t>169129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253064</t>
+          <t>253143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299765</t>
+          <t>302756</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>498765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>529448</t>
+          <t>531054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>512819</t>
+          <t>515474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>548899</t>
+          <t>548143</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1023694</t>
+          <t>1020703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1070395</t>
+          <t>1070316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,87%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30160</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28418</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54165</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>59963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61345</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75018</t>
+          <t>74704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125532</t>
+          <t>126080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144400</t>
+          <t>145358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>31876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50484</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60876</t>
+          <t>60715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74667</t>
+          <t>74646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73180</t>
+          <t>74023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85405</t>
+          <t>85005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138260</t>
+          <t>138257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156199</t>
+          <t>156106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32271</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50082</t>
+          <t>49670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57374</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70789</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60641</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74087</t>
+          <t>73769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122202</t>
+          <t>122614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140013</t>
+          <t>140790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>37077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>48931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>70621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92178</t>
+          <t>91802</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121403</t>
+          <t>120016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148561</t>
+          <t>149272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168612</t>
+          <t>169031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158918</t>
+          <t>157485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180552</t>
+          <t>179175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>312810</t>
+          <t>314197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342035</t>
+          <t>342411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25917</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43355</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21844</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38505</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75152</t>
+          <t>75305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105814</t>
+          <t>106838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123252</t>
+          <t>123880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100813</t>
+          <t>100879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117540</t>
+          <t>117036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213401</t>
+          <t>213248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>237013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34441</t>
+          <t>34609</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39276</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>48211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62913</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108443</t>
+          <t>108540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141208</t>
+          <t>142388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177096</t>
+          <t>176031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145757</t>
+          <t>144130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180586</t>
+          <t>180956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>292001</t>
+          <t>293800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>345849</t>
+          <t>347601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>500010</t>
+          <t>501075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>535898</t>
+          <t>534718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>533749</t>
+          <t>533379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>568578</t>
+          <t>570205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1045592</t>
+          <t>1043840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1099440</t>
+          <t>1097641</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52995</t>
+          <t>52734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68379</t>
+          <t>68183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68311</t>
+          <t>67895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81640</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128573</t>
+          <t>128834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147401</t>
+          <t>147877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>31403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49660</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82592</t>
+          <t>81841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94200</t>
+          <t>94512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81750</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95736</t>
+          <t>96506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168150</t>
+          <t>168460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187035</t>
+          <t>186407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46970</t>
+          <t>46848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55996</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60253</t>
+          <t>60311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70427</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110298</t>
+          <t>110939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123853</t>
+          <t>124603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40994</t>
+          <t>40488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60367</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>81622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109685</t>
+          <t>108377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162514</t>
+          <t>162680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181887</t>
+          <t>182393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154057</t>
+          <t>155427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174732</t>
+          <t>173925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322744</t>
+          <t>324052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>350156</t>
+          <t>350807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35494</t>
+          <t>35445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20754</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>68162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100700</t>
+          <t>100749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116077</t>
+          <t>116221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104854</t>
+          <t>105146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121016</t>
+          <t>121264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>211069</t>
+          <t>209802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232007</t>
+          <t>232231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43871</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>53789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>50916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>61603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99794</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113647</t>
+          <t>113744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118491</t>
+          <t>119134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151220</t>
+          <t>151050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121005</t>
+          <t>120937</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>154749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250078</t>
+          <t>251228</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299448</t>
+          <t>295490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>518981</t>
+          <t>519151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>551710</t>
+          <t>551067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>550293</t>
+          <t>551001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>584745</t>
+          <t>584813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1076503</t>
+          <t>1080461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1125873</t>
+          <t>1124723</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,74%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>28232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34618</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57543</t>
+          <t>58282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71046</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86986</t>
+          <t>86945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>108676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122872</t>
+          <t>123239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>183088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206752</t>
+          <t>206025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78381</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88061</t>
+          <t>88756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>72115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84625</t>
+          <t>84996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154432</t>
+          <t>154208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170371</t>
+          <t>171027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44585</t>
+          <t>44936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50588</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>57523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94200</t>
+          <t>95052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106669</t>
+          <t>106799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>41007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52026</t>
+          <t>52519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>55381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87293</t>
+          <t>85893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176209</t>
+          <t>177003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198706</t>
+          <t>198938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166246</t>
+          <t>165753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186701</t>
+          <t>186841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348989</t>
+          <t>350389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380528</t>
+          <t>380901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28833</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>39357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61885</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105428</t>
+          <t>105307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123004</t>
+          <t>122106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141563</t>
+          <t>141716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220160</t>
+          <t>219608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243848</t>
+          <t>242688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>54202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>53302</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>65056</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111594</t>
+          <t>111662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126730</t>
+          <t>126241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82362</t>
+          <t>80551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116461</t>
+          <t>117266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112438</t>
+          <t>109852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151780</t>
+          <t>149438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203552</t>
+          <t>204246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253277</t>
+          <t>255160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>540876</t>
+          <t>540071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>574975</t>
+          <t>576786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>597445</t>
+          <t>599787</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636787</t>
+          <t>639373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1153286</t>
+          <t>1151403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1203011</t>
+          <t>1202317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
